--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260908.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260908.xlsx
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
